--- a/01_Thermal/B_results/four_annular_bemt_analysis.xlsx
+++ b/01_Thermal/B_results/four_annular_bemt_analysis.xlsx
@@ -506,28 +506,28 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>45.26546653804171</v>
+        <v>45.54596580607951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2752530234590583</v>
+        <v>0.3175862263792186</v>
       </c>
       <c r="G2" t="n">
-        <v>322.7931675201226</v>
+        <v>189.007685055349</v>
       </c>
       <c r="H2" t="n">
-        <v>4260.495759386248</v>
+        <v>1873.942000315514</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07701016443093317</v>
+        <v>0.07591572344745157</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2958436158686003</v>
+        <v>0.2980328955768706</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1624745274719971</v>
+        <v>0.1591619568173999</v>
       </c>
       <c r="L2" t="n">
-        <v>8.302601624292414</v>
+        <v>8.307777184084769</v>
       </c>
     </row>
     <row r="3">
@@ -546,28 +546,28 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>50.35696132577613</v>
+        <v>49.80407487951953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3221457738756169</v>
+        <v>0.3034959008063034</v>
       </c>
       <c r="G3" t="n">
-        <v>572.1158147915559</v>
+        <v>203.4636856407884</v>
       </c>
       <c r="H3" t="n">
-        <v>5512.886817461289</v>
+        <v>2208.926411826067</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05925107008653921</v>
+        <v>0.06712194658915376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3042095106910765</v>
+        <v>0.3264615168188679</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3017640448444596</v>
+        <v>0.2713357029532429</v>
       </c>
       <c r="L3" t="n">
-        <v>3.673468898514652</v>
+        <v>3.627882881487762</v>
       </c>
     </row>
     <row r="4">
@@ -586,28 +586,28 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>53.4665672817809</v>
+        <v>53.57835189932899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3702845312963785</v>
+        <v>0.3915267848900723</v>
       </c>
       <c r="G4" t="n">
-        <v>516.4539295781068</v>
+        <v>316.4576492066899</v>
       </c>
       <c r="H4" t="n">
-        <v>3766.694924158668</v>
+        <v>2064.394253198892</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05762570622256651</v>
+        <v>0.07245628000544568</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3965186687979672</v>
+        <v>0.4079876049489706</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3011180901737099</v>
+        <v>0.2733801669170738</v>
       </c>
       <c r="L4" t="n">
-        <v>2.685617718751482</v>
+        <v>2.631578508213393</v>
       </c>
     </row>
     <row r="5">
@@ -626,28 +626,28 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>53.07656592600134</v>
+        <v>53.00355493518373</v>
       </c>
       <c r="F5" t="n">
-        <v>0.367339542503838</v>
+        <v>0.3228267664976978</v>
       </c>
       <c r="G5" t="n">
-        <v>2312.23055192135</v>
+        <v>818.6379775166715</v>
       </c>
       <c r="H5" t="n">
-        <v>17135.46024586531</v>
+        <v>7855.11985311939</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09299007972365048</v>
+        <v>0.08588291627640322</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5001969010415416</v>
+        <v>0.5031487664939811</v>
       </c>
       <c r="K5" t="n">
-        <v>0.239521224470628</v>
+        <v>0.2463474029469355</v>
       </c>
       <c r="L5" t="n">
-        <v>2.653443197058862</v>
+        <v>2.665509275347747</v>
       </c>
     </row>
     <row r="6">
@@ -666,28 +666,28 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>54.14268425899471</v>
+        <v>54.15257348849804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3445698622118334</v>
+        <v>0.366018570107608</v>
       </c>
       <c r="G6" t="n">
-        <v>848.9985100122119</v>
+        <v>742.754386688109</v>
       </c>
       <c r="H6" t="n">
-        <v>7150.76242849565</v>
+        <v>5544.201235342096</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03362973376737285</v>
+        <v>0.04685351371269286</v>
       </c>
       <c r="J6" t="n">
-        <v>0.353109939738547</v>
+        <v>0.3489196310853024</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5917131525471122</v>
+        <v>0.5636336542090371</v>
       </c>
       <c r="L6" t="n">
-        <v>1.764770227515085</v>
+        <v>1.739179236955575</v>
       </c>
     </row>
     <row r="7">
@@ -706,28 +706,28 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>39.82536718249986</v>
+        <v>39.74450779042364</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3040756077346039</v>
+        <v>0.2812467964345271</v>
       </c>
       <c r="G7" t="n">
-        <v>629.3529764986603</v>
+        <v>501.201892305182</v>
       </c>
       <c r="H7" t="n">
-        <v>6806.614016268456</v>
+        <v>6336.326293623866</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02817087618226947</v>
+        <v>0.0257432361284092</v>
       </c>
       <c r="J7" t="n">
-        <v>0.24724377293904</v>
+        <v>0.2473770796282853</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7363249806728098</v>
+        <v>0.7482540721475065</v>
       </c>
       <c r="L7" t="n">
-        <v>1.327701184492657</v>
+        <v>1.31581736879304</v>
       </c>
     </row>
     <row r="8">
@@ -746,28 +746,28 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>42.09556680347002</v>
+        <v>42.19864612819604</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2839633934147522</v>
+        <v>0.2871950925902123</v>
       </c>
       <c r="G8" t="n">
-        <v>411.056859568306</v>
+        <v>449.0088934449186</v>
       </c>
       <c r="H8" t="n">
-        <v>5097.734174531417</v>
+        <v>5443.784362382622</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03077311069516335</v>
+        <v>0.03421492554610046</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2540441644259578</v>
+        <v>0.2526391832792384</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9103135230012898</v>
+        <v>0.908461995245136</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8669765830689999</v>
+        <v>0.8570443537611195</v>
       </c>
     </row>
     <row r="9">
@@ -782,16 +782,16 @@
         <v>1365</v>
       </c>
       <c r="E9" t="n">
-        <v>338.2291793165647</v>
+        <v>338.0276749272295</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3359584202335988</v>
+        <v>0.3206317574904545</v>
       </c>
       <c r="G9" t="n">
-        <v>5613.001809890314</v>
+        <v>3220.532169857708</v>
       </c>
       <c r="H9" t="n">
-        <v>49730.64836616704</v>
+        <v>31326.69440980845</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
